--- a/data/output/2025/evaluasi_95.xlsx
+++ b/data/output/2025/evaluasi_95.xlsx
@@ -1567,7 +1567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2117,18 +2117,410 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>-17.43577937619188</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>51.97553859851934</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.556242462953815</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-48.04924819489001</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.978957116227114</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-13.65758911027666</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-12.15684314024616</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.259325042957969</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>41.20892385978656</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3707334978473555</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>45.18501713517942</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.48623951194367</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.4895848555142306</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.02341370642866151</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9502</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kabupaten Boven Digoel</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>7.199875591702159</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2145,7 +2537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2737,6 +3129,342 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.1435855255452625</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3.404777700613794</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.378258149574855</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>35.45633410926414</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-27.35412491093971</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-27.87694480604059</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>37.63219577024346</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-10.13331801513127</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-5.7355832694024</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2363182856689683</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1.083978265382346</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>9503</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kabupaten Mappi</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.9948706208239689</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2751,7 +3479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3161,18 +3889,382 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>22.81054963671199</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9.77812061760762</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>74.74281130915712</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>36.54512423762537</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8.281262678662129</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-40.06650290793972</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>56.82040766974612</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>59.92799248628342</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-20.10758894645115</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>47.98211774495055</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3680476018686708</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.425895528183928</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8.312508969233097</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9501</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Merauke</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>5.964112564589428</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3189,7 +4281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3739,18 +4831,270 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>51.81916105705564</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.7366240967124</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>35.66675482519611</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.051472037036393</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>45.38009359454958</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3281197054695372</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.056805401101937</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8524924892236546</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7.364180238433947</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9504</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Asmat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>5.4534726439985</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
